--- a/config/excel/CfgEncounters.xlsx
+++ b/config/excel/CfgEncounters.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEncounters" sheetId="1" r:id="Rbb9d0cad750248a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CfgEncounters" sheetId="1" r:id="R8ab464ac69aa4d4c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -35,6 +35,11 @@
       <x:sz val="10"/>
       <x:color rgb="FF215E99"/>
       <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF215E99"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
   <x:fills count="5">
@@ -66,7 +71,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -93,6 +98,7 @@
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -583,6 +589,126 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="36" customHeight="1">
+      <x:c r="A15" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B15" s="10" t="str">
+        <x:v>mob_cover</x:v>
+      </x:c>
+      <x:c r="C15" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="36" customHeight="1">
+      <x:c r="A16" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="10" t="str">
+        <x:v>mob_stagger</x:v>
+      </x:c>
+      <x:c r="C16" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="36" customHeight="1">
+      <x:c r="A17" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B17" s="10" t="str">
+        <x:v>mob_cover</x:v>
+      </x:c>
+      <x:c r="C17" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E17" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F17" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="36" customHeight="1">
+      <x:c r="A18" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B18" s="10" t="str">
+        <x:v>mob_stagger</x:v>
+      </x:c>
+      <x:c r="C18" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="36" customHeight="1">
+      <x:c r="A19" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="10" t="str">
+        <x:v>mob_cover</x:v>
+      </x:c>
+      <x:c r="C19" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E19" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="36" customHeight="1">
+      <x:c r="A20" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="10" t="str">
+        <x:v>mob_stagger</x:v>
+      </x:c>
+      <x:c r="C20" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
